--- a/problems/marketing/4.coupon_roi/eval/answer_key/summary_answer.xlsx
+++ b/problems/marketing/4.coupon_roi/eval/answer_key/summary_answer.xlsx
@@ -459,24 +459,24 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>행 단위</t>
+          <t>이 표는 무엇인가요</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전체 요약 = 단 1행. 모든 쿠폰을 합산한 전사(全社) 성과</t>
+          <t>전체 요약은 딱 1줄입니다. 모든 쿠폰을 합친 회사 전체 성과를 적어요.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>무엇을 보고 채우나요</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>data/coupon_roi_given.xlsx (★제공된 정답 집계표). 1단계 집계를 틀려도 2단계는 영향 없음</t>
+          <t>데이터/정리된_쿠폰성과표_참고용.xlsx (미리 정리해 둔 쿠폰별 성과표). 1단계 표를 틀렸어도 이 파일만 보고 풀 수 있습니다.</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>모든 쿠폰의 사용건수/매출합계/할인합계 합(정수)</t>
+          <t>모든 쿠폰의 사용건수/매출합계/할인합계를 각각 전부 더한 값</t>
         </is>
       </c>
     </row>
@@ -500,19 +500,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>모든 쿠폰의 공헌이익/순이익 합(정수)</t>
+          <t>모든 쿠폰의 공헌이익/순이익을 각각 전부 더한 값</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>★전체ROI</t>
+          <t>★전체ROI (주의)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>총순이익 / 총할인 × 100 (가중). 쿠폰별 ROI의 단순평균이 아니다 — 할인이 큰 쿠폰이 더 큰 가중을 갖는다. 소수 첫째 자리 반올림</t>
+          <t>총순이익 ÷ 총할인 × 100 으로 계산합니다. 쿠폰별 ROI 를 그냥 평균 내면 안 돼요 — 할인을 많이 쓴 쿠폰이 더 크게 반영돼야 맞습니다. 소수 첫째 자리에서 반올림.</t>
         </is>
       </c>
     </row>
@@ -524,31 +524,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>순이익 &lt; 0 인 쿠폰의 개수(정수)</t>
+          <t>순이익이 0보다 작은(적자인) 쿠폰이 몇 개인지 센 값</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>★반올림/허용오차</t>
+          <t>★숫자 정확도</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ROI는 소수 첫째 자리 반올림, 채점 허용오차 ±0.1. 합계·개수는 정수 정확</t>
+          <t>ROI 는 ±0.1 까지 봐주고, 합계와 개수는 정확히 맞아야 정답입니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>★단순평균 함정</t>
+          <t>★자주 하는 실수</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>전체ROI를 '쿠폰 ROI들의 평균'으로 내면 오답 — 반드시 총순이익/총할인</t>
+          <t>전체ROI 를 '쿠폰들의 ROI 평균'으로 내면 틀립니다. 반드시 총순이익 ÷ 총할인.</t>
         </is>
       </c>
     </row>
